--- a/volunteer_forms/021_parent_volunteer_consent_form--volunteer_forms.xlsx
+++ b/volunteer_forms/021_parent_volunteer_consent_form--volunteer_forms.xlsx
@@ -1,15 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -32,7 +31,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -43,12 +42,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="004472C4"/>
         <bgColor rgb="004472C4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0070AD47"/>
-        <bgColor rgb="0070AD47"/>
       </patternFill>
     </fill>
   </fills>
@@ -64,12 +57,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -437,12 +427,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -531,7 +521,7 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -554,7 +544,7 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -577,30 +567,30 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>communication_preferences</t>
+          <t>emergency_contact</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Communication Preferences</t>
+          <t>Emergency Contact</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -612,41 +602,41 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>emergency_contact</t>
+          <t>volunteer_agreement</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Emergency Contact</t>
+          <t>Volunteer Agreement</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>volunteer_activities</t>
+          <t>additional_comments</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Volunteer Activities</t>
+          <t>Additional Comments</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -658,12 +648,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>volunteer_agreement</t>
+          <t>signature</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Volunteer Agreement</t>
+          <t>Signature</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,18 +671,18 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>additional_comments</t>
+          <t>parent_volunteer_consent</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Additional Comments</t>
+          <t>Parent Volunteer Consent</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -704,18 +694,18 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>signature</t>
+          <t>signature_1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Signature 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -727,12 +717,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>signature_1</t>
+          <t>signature_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Signature 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +740,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>signature_2</t>
+          <t>signature_3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Signature 3</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,317 +763,18 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>signature_3</t>
+          <t>signature_4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Signature 4</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>signature_4</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>signature_5</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>signature_6</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>signature_7</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>signature_8</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>signature_9</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>signature_10</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>signature_11</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>signature_12</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>signature_13</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>signature_14</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>signature_15</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>parent_volunteer_consent</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Parent Volunteer Consent</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1093,246 +784,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>list_name</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>label</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>communication_preferences_choices</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>communication_preferences_choices</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>communication_preferences_choices</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>communication_preferences_choices</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>volunteer_activities_choices</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>activity1</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>activity1</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>volunteer_activities_choices</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>activity2</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>activity2</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>volunteer_activities_choices</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>activity3</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>activity3</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>volunteer_activities_choices</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>activity4</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>activity4</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>volunteer_activities_choices</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>activity5</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>activity5</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>volunteer_activities_choices</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>activity6</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>activity6</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>volunteer_activities_choices</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>activity7</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>activity7</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>volunteer_activities_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>activity8</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>activity8</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
